--- a/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T10:12:02+00:00</t>
+    <t>2025-01-28T14:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
     <t>Slot.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(HealthcareService)
+    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -512,7 +512,10 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the Schedule resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -551,7 +554,7 @@
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Schedule)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-schedule)
 </t>
   </si>
   <si>
@@ -943,7 +946,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="111.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -958,7 +961,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.80859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2366,11 +2369,11 @@
         <v>18</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -2414,10 +2417,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2443,10 +2446,10 @@
         <v>149</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2473,13 +2476,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2497,7 +2500,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2523,10 +2526,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2552,13 +2555,13 @@
         <v>149</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2584,11 +2587,11 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2606,7 +2609,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2632,10 +2635,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2658,13 +2661,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2715,7 +2718,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>84</v>
@@ -2741,10 +2744,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2770,10 +2773,10 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2803,10 +2806,10 @@
         <v>108</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -2824,7 +2827,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
@@ -2845,15 +2848,15 @@
         <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2876,13 +2879,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2933,7 +2936,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -2948,21 +2951,21 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2985,13 +2988,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3042,7 +3045,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3057,21 +3060,21 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3094,13 +3097,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3108,7 +3111,7 @@
         <v>18</v>
       </c>
       <c r="Q20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>18</v>
@@ -3153,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3179,10 +3182,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3205,13 +3208,13 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3262,7 +3265,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
